--- a/fcr-generator/fcr_template.xlsx
+++ b/fcr-generator/fcr_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Z005BYAE\Documents\fcr_ws\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Z005BYAE\Documents\fcr_ws\fcr-generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B24FF9-0448-412C-AED4-34A004B6F75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED12DC7-0F94-4E32-A021-3B4B0F5BCF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>日期：</t>
   </si>
   <si>
-    <t xml:space="preserve">Siemens High Voltage Switchgear Co., Ltd. Shanghai         </t>
+    <t>Mock Ltd.</t>
   </si>
 </sst>
 </file>
@@ -201,25 +201,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -242,31 +242,31 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>689563</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>59055</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="siemens-energy.com">
+        <xdr:cNvPr id="3" name="Picture 2" descr="Mock Logo - 素材 - Canva可画">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F799680-A5A9-17C2-1A5C-F57E6D0EFB4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5B6FF86-58A6-A0AC-8F50-F4C91C272B35}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" r:link="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -280,16 +280,22 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="76200" y="9525"/>
-          <a:ext cx="974725" cy="506730"/>
+          <a:off x="95250" y="47624"/>
+          <a:ext cx="594313" cy="514351"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -574,37 +580,37 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1">
       <c r="A1" s="3"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -637,10 +643,10 @@
     <row r="6" spans="1:8">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="7" t="s">
@@ -720,19 +726,19 @@
       <c r="A14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
       <c r="F14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="4" t="s">
@@ -818,43 +824,43 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4"/>
@@ -998,6 +1004,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="G28:H28"/>
@@ -1014,28 +1042,6 @@
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
